--- a/model_results.xlsx
+++ b/model_results.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MSAI&amp;I\semester2\MSI5102 ML Essentials\Algorithms\project\MSI5102_project_code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86880D20-4262-4AA3-9ABA-FE95901B456D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A6AFA6-6E11-4F01-B89F-57992477E4F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Machine_learning_approach" sheetId="1" r:id="rId1"/>
+    <sheet name="Deep_learning_approach" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Model</t>
   </si>
@@ -61,13 +62,61 @@
   </si>
   <si>
     <t xml:space="preserve">Random Forest </t>
+  </si>
+  <si>
+    <t>train_acc</t>
+  </si>
+  <si>
+    <t>test_acc</t>
+  </si>
+  <si>
+    <t>precision</t>
+  </si>
+  <si>
+    <t>recall</t>
+  </si>
+  <si>
+    <t>f1</t>
+  </si>
+  <si>
+    <t>gen_gap</t>
+  </si>
+  <si>
+    <t>Baseline Dense</t>
+  </si>
+  <si>
+    <t>L2 Regularization</t>
+  </si>
+  <si>
+    <t>L1 Regularization</t>
+  </si>
+  <si>
+    <t>ElasticNet</t>
+  </si>
+  <si>
+    <t>Dropout</t>
+  </si>
+  <si>
+    <t>Batch Normalization</t>
+  </si>
+  <si>
+    <t>Early Stopping</t>
+  </si>
+  <si>
+    <t>LR Decay</t>
+  </si>
+  <si>
+    <t>CNN</t>
+  </si>
+  <si>
+    <t>Method</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -86,16 +135,35 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -118,16 +186,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -556,4 +648,249 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67DE2C6B-F96E-4CD9-B323-4BA8A631DFFE}">
+  <dimension ref="A2:G11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="25.6328125" customWidth="1"/>
+    <col min="2" max="7" width="21.90625" customWidth="1"/>
+    <col min="8" max="8" width="21.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0.97589999999999999</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.96009999999999995</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.95940000000000003</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.96</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.95960000000000001</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1.5800000000000002E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0.96879999999999999</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.9577</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.95779999999999998</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.95709999999999995</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0.95689999999999997</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1.11E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0.95920000000000005</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.95879999999999999</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.95899999999999996</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.95799999999999996</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.95830000000000004</v>
+      </c>
+      <c r="G5" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.95830000000000004</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.95289999999999997</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.95309999999999995</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.95250000000000001</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.9526</v>
+      </c>
+      <c r="G6" s="3">
+        <v>5.4000000000000003E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.69010000000000005</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.69510000000000005</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.71020000000000005</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.68989999999999996</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.65429999999999999</v>
+      </c>
+      <c r="G7" s="3">
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.9909</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.97670000000000001</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.97660000000000002</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.97650000000000003</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.97650000000000003</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1.4200000000000001E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.97219999999999995</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.96509999999999996</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.9647</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.96479999999999999</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.9647</v>
+      </c>
+      <c r="G9" s="3">
+        <v>7.1000000000000004E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.98570000000000002</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.97019999999999995</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.97040000000000004</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.9698</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.97</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1.55E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0.98350000000000004</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.98360000000000003</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.98329999999999995</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.98340000000000005</v>
+      </c>
+      <c r="G11" s="3">
+        <v>8.5000000000000006E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/model_results.xlsx
+++ b/model_results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MSAI&amp;I\semester2\MSI5102 ML Essentials\Algorithms\project\MSI5102_project_code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4767dece47506b4d/Attachments/ML_essential_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A6AFA6-6E11-4F01-B89F-57992477E4F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{11A6AFA6-6E11-4F01-B89F-57992477E4F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A246896-6E11-4260-8F8A-21E39EA2FBC1}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Machine_learning_approach" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>Model</t>
   </si>
@@ -85,31 +85,28 @@
     <t>Baseline Dense</t>
   </si>
   <si>
-    <t>L2 Regularization</t>
-  </si>
-  <si>
-    <t>L1 Regularization</t>
-  </si>
-  <si>
-    <t>ElasticNet</t>
-  </si>
-  <si>
-    <t>Dropout</t>
-  </si>
-  <si>
-    <t>Batch Normalization</t>
-  </si>
-  <si>
-    <t>Early Stopping</t>
-  </si>
-  <si>
-    <t>LR Decay</t>
-  </si>
-  <si>
-    <t>CNN</t>
-  </si>
-  <si>
-    <t>Method</t>
+    <t>CNN (base)</t>
+  </si>
+  <si>
+    <t>CNN + LR Decay</t>
+  </si>
+  <si>
+    <t>CNN + BatchNorm</t>
+  </si>
+  <si>
+    <t>CNN + Dropout</t>
+  </si>
+  <si>
+    <t>CNN + Early Stopping</t>
+  </si>
+  <si>
+    <t>CNN + L2</t>
+  </si>
+  <si>
+    <t>CNN + Data Augmentation</t>
+  </si>
+  <si>
+    <t>CNN + L1</t>
   </si>
 </sst>
 </file>
@@ -216,11 +213,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -661,210 +658,210 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.4">
-      <c r="A2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="3">
-        <v>0.97589999999999999</v>
+        <v>0.99660000000000004</v>
       </c>
       <c r="C3" s="3">
-        <v>0.96009999999999995</v>
+        <v>0.99080000000000001</v>
       </c>
       <c r="D3" s="3">
-        <v>0.95940000000000003</v>
+        <v>0.99080000000000001</v>
       </c>
       <c r="E3" s="3">
-        <v>0.96</v>
+        <v>0.99070000000000003</v>
       </c>
       <c r="F3" s="3">
-        <v>0.95960000000000001</v>
+        <v>0.99070000000000003</v>
       </c>
       <c r="G3" s="3">
-        <v>1.5800000000000002E-2</v>
+        <v>5.7999999999999996E-3</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="3">
-        <v>0.96879999999999999</v>
+        <v>0.99660000000000004</v>
       </c>
       <c r="C4" s="3">
-        <v>0.9577</v>
+        <v>0.9899</v>
       </c>
       <c r="D4" s="3">
-        <v>0.95779999999999998</v>
+        <v>0.98980000000000001</v>
       </c>
       <c r="E4" s="3">
-        <v>0.95709999999999995</v>
+        <v>0.98970000000000002</v>
       </c>
       <c r="F4" s="3">
-        <v>0.95689999999999997</v>
+        <v>0.98980000000000001</v>
       </c>
       <c r="G4" s="3">
-        <v>1.11E-2</v>
+        <v>6.7000000000000002E-3</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5" s="3">
-        <v>0.95920000000000005</v>
+        <v>0.99590000000000001</v>
       </c>
       <c r="C5" s="3">
-        <v>0.95879999999999999</v>
+        <v>0.98960000000000004</v>
       </c>
       <c r="D5" s="3">
-        <v>0.95899999999999996</v>
+        <v>0.98970000000000002</v>
       </c>
       <c r="E5" s="3">
-        <v>0.95799999999999996</v>
+        <v>0.98950000000000005</v>
       </c>
       <c r="F5" s="3">
-        <v>0.95830000000000004</v>
+        <v>0.98950000000000005</v>
       </c>
       <c r="G5" s="3">
-        <v>5.0000000000000001E-4</v>
+        <v>6.3E-3</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3">
-        <v>0.95830000000000004</v>
+        <v>0.99029999999999996</v>
       </c>
       <c r="C6" s="3">
-        <v>0.95289999999999997</v>
+        <v>0.98860000000000003</v>
       </c>
       <c r="D6" s="3">
-        <v>0.95309999999999995</v>
+        <v>0.98860000000000003</v>
       </c>
       <c r="E6" s="3">
-        <v>0.95250000000000001</v>
+        <v>0.98850000000000005</v>
       </c>
       <c r="F6" s="3">
-        <v>0.9526</v>
+        <v>0.98850000000000005</v>
       </c>
       <c r="G6" s="3">
-        <v>5.4000000000000003E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" s="3">
-        <v>0.69010000000000005</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="C7" s="3">
-        <v>0.69510000000000005</v>
+        <v>0.98699999999999999</v>
       </c>
       <c r="D7" s="3">
-        <v>0.71020000000000005</v>
+        <v>0.98709999999999998</v>
       </c>
       <c r="E7" s="3">
-        <v>0.68989999999999996</v>
+        <v>0.9869</v>
       </c>
       <c r="F7" s="3">
-        <v>0.65429999999999999</v>
+        <v>0.98699999999999999</v>
       </c>
       <c r="G7" s="3">
-        <v>-5.0000000000000001E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" s="3">
-        <v>0.9909</v>
+        <v>0.98860000000000003</v>
       </c>
       <c r="C8" s="3">
-        <v>0.97670000000000001</v>
+        <v>0.98540000000000005</v>
       </c>
       <c r="D8" s="3">
-        <v>0.97660000000000002</v>
+        <v>0.98550000000000004</v>
       </c>
       <c r="E8" s="3">
-        <v>0.97650000000000003</v>
+        <v>0.98519999999999996</v>
       </c>
       <c r="F8" s="3">
-        <v>0.97650000000000003</v>
+        <v>0.98519999999999996</v>
       </c>
       <c r="G8" s="3">
-        <v>1.4200000000000001E-2</v>
+        <v>3.2000000000000002E-3</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="3">
-        <v>0.97219999999999995</v>
+        <v>0.98619999999999997</v>
       </c>
       <c r="C9" s="3">
-        <v>0.96509999999999996</v>
+        <v>0.98309999999999997</v>
       </c>
       <c r="D9" s="3">
-        <v>0.9647</v>
+        <v>0.98329999999999995</v>
       </c>
       <c r="E9" s="3">
-        <v>0.96479999999999999</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="F9" s="3">
-        <v>0.9647</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="G9" s="3">
-        <v>7.1000000000000004E-3</v>
+        <v>3.0999999999999999E-3</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B10" s="3">
-        <v>0.98570000000000002</v>
+        <v>0.99019999999999997</v>
       </c>
       <c r="C10" s="3">
-        <v>0.97019999999999995</v>
+        <v>0.97650000000000003</v>
       </c>
       <c r="D10" s="3">
-        <v>0.97040000000000004</v>
+        <v>0.97670000000000001</v>
       </c>
       <c r="E10" s="3">
-        <v>0.9698</v>
+        <v>0.97640000000000005</v>
       </c>
       <c r="F10" s="3">
-        <v>0.97</v>
+        <v>0.97640000000000005</v>
       </c>
       <c r="G10" s="3">
-        <v>1.55E-2</v>
+        <v>1.37E-2</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -872,22 +869,22 @@
         <v>26</v>
       </c>
       <c r="B11" s="3">
-        <v>0.99199999999999999</v>
+        <v>0.97360000000000002</v>
       </c>
       <c r="C11" s="3">
-        <v>0.98350000000000004</v>
+        <v>0.97589999999999999</v>
       </c>
       <c r="D11" s="3">
-        <v>0.98360000000000003</v>
+        <v>0.9758</v>
       </c>
       <c r="E11" s="3">
-        <v>0.98329999999999995</v>
+        <v>0.9758</v>
       </c>
       <c r="F11" s="3">
-        <v>0.98340000000000005</v>
+        <v>0.97570000000000001</v>
       </c>
       <c r="G11" s="3">
-        <v>8.5000000000000006E-3</v>
+        <v>-2.3E-3</v>
       </c>
     </row>
   </sheetData>
